--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465390</v>
       </c>
       <c r="B2" t="n">
-        <v>92682</v>
+        <v>92684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128465389</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>92295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128465391</v>
       </c>
       <c r="B4" t="n">
-        <v>92682</v>
+        <v>92684</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465390</v>
       </c>
       <c r="B2" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128465389</v>
       </c>
       <c r="B3" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128465391</v>
       </c>
       <c r="B4" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465390</v>
       </c>
       <c r="B2" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128465389</v>
       </c>
       <c r="B3" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128465391</v>
       </c>
       <c r="B4" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465390</v>
       </c>
       <c r="B2" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128465389</v>
       </c>
       <c r="B3" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128465391</v>
       </c>
       <c r="B4" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465390</v>
       </c>
       <c r="B2" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128465389</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128465391</v>
       </c>
       <c r="B4" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465390</v>
       </c>
       <c r="B2" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128465389</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128465391</v>
       </c>
       <c r="B4" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465390</v>
       </c>
       <c r="B2" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128465389</v>
       </c>
       <c r="B3" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128465391</v>
       </c>
       <c r="B4" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465390</v>
       </c>
       <c r="B2" t="n">
-        <v>92818</v>
+        <v>92830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128465389</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128465391</v>
       </c>
       <c r="B4" t="n">
-        <v>92818</v>
+        <v>92830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465390</v>
       </c>
       <c r="B2" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128465389</v>
       </c>
       <c r="B3" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128465391</v>
       </c>
       <c r="B4" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465390</v>
       </c>
       <c r="B2" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128465389</v>
       </c>
       <c r="B3" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>128465391</v>
       </c>
       <c r="B4" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128465390</v>
+        <v>422177</v>
       </c>
       <c r="B2" t="n">
-        <v>92842</v>
+        <v>101947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>1449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Hällebräcka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Saxifraga osloënsis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+          <t>Ramdalen, 600 m VSV om, vägskärning, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346741</v>
+        <v>346774</v>
       </c>
       <c r="R2" t="n">
-        <v>6529587</v>
+        <v>6529551</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,14 +747,24 @@
           <t>Tisselskog</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>OD-Ben-0182</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2001-12-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 m2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,29 +773,37 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Sydvänd vägskärning på enskilda vägen till Ramdalen</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Dalsland Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128465389</v>
+        <v>7069886</v>
       </c>
       <c r="B3" t="n">
-        <v>92451</v>
+        <v>89143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +811,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>4405</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+          <t>Dackehögen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346718</v>
+        <v>346620</v>
       </c>
       <c r="R3" t="n">
-        <v>6529597</v>
+        <v>6529618</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -841,12 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2013-10-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2013-10-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -855,28 +881,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Jan  Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Jan  Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128465391</v>
+        <v>128465389</v>
       </c>
       <c r="B4" t="n">
-        <v>92842</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,37 +911,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norr om Dackehöjdens naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346754</v>
+        <v>346718</v>
       </c>
       <c r="R4" t="n">
-        <v>6529578</v>
+        <v>6529597</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -955,7 +979,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -971,6 +994,803 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128465419</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>346632</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6529633</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128465417</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>346621</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6529622</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7069885</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dackehögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>346625</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6529630</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2013-10-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2013-10-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan  Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan  Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112195875</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dackehögen, väster om NR, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>346614</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6529634</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Anita Stridvall, Jan  Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128465390</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>346741</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6529587</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128465391</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>346754</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6529578</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128465393</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>346765</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6529577</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128465418</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>346633</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6529629</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41407-2025 artfynd.xlsx
+++ b/artfynd/A 41407-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/422177</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7069886</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465389</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465419</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465417</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7069885</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112195875</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465390</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465391</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1694,6 +1744,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465393</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,8 +1846,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465418</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>